--- a/EXCEL/class notes/day5 data validation/Data Validation Indirect V1.xlsx
+++ b/EXCEL/class notes/day5 data validation/Data Validation Indirect V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day5 data validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E59057E-923C-48E6-AB6F-48F34AFD0C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E9082E-29EC-47FF-AF3F-9C8E5381813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FCEC9138-7022-457F-8408-57A88E058698}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FCEC9138-7022-457F-8408-57A88E058698}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -766,9 +775,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C102D752-636F-4A0D-8810-EEB9672C7546}">
   <dimension ref="B3:L18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>36</v>
       </c>
@@ -777,17 +786,17 @@
         <v>Test</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D6" s="1" t="s">
         <v>1</v>
       </c>
@@ -808,7 +817,7 @@
         <v>$B$3</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
@@ -828,7 +837,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D8" s="1" t="s">
         <v>11</v>
       </c>
@@ -845,7 +854,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D9" s="1" t="s">
         <v>16</v>
       </c>
@@ -862,29 +871,29 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L10" t="str">
         <f ca="1">INDIRECT(L6)</f>
         <v>Test</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
         <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
         <v>21</v>
       </c>
@@ -895,12 +904,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H16" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F18" s="3" t="s">
         <v>22</v>
       </c>
@@ -924,24 +933,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76475CB0-2A31-4BCA-B9C9-837594108C58}">
   <dimension ref="C4:E10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C4" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C5" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C8" s="2">
         <f>SUM(C4:C6)</f>
         <v>45</v>
@@ -951,7 +960,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>41</v>
       </c>
@@ -967,9 +976,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C681AF40-F2CD-4486-A44A-23DBA5A46C9E}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>21</v>
       </c>
@@ -980,7 +989,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1001</v>
       </c>
@@ -991,7 +1000,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1002</v>
       </c>
@@ -1000,10 +1009,10 @@
       </c>
       <c r="C3" s="13">
         <f t="shared" ref="C3:C11" ca="1" si="0">RANDBETWEEN(1,100)</f>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>1003</v>
       </c>
@@ -1012,16 +1021,16 @@
       </c>
       <c r="C4" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="1">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>1004</v>
       </c>
@@ -1030,17 +1039,17 @@
       </c>
       <c r="C5" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="17" t="str">
         <f>VLOOKUP(ID,BaseTbl,2,0)</f>
-        <v>Nme9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>Nme3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>1005</v>
       </c>
@@ -1049,17 +1058,17 @@
       </c>
       <c r="C6" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
       </c>
       <c r="G6" s="2">
         <f ca="1">VLOOKUP(ID,BaseTbl,3,0)</f>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>1006</v>
       </c>
@@ -1068,10 +1077,10 @@
       </c>
       <c r="C7" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>1007</v>
       </c>
@@ -1080,13 +1089,13 @@
       </c>
       <c r="C8" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="G8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>1008</v>
       </c>
@@ -1095,10 +1104,10 @@
       </c>
       <c r="C9" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>1009</v>
       </c>
@@ -1107,10 +1116,10 @@
       </c>
       <c r="C10" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>1010</v>
       </c>
@@ -1119,7 +1128,7 @@
       </c>
       <c r="C11" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
